--- a/src/MoleNet_7.0/Tests/Power Measurements.xlsx
+++ b/src/MoleNet_7.0/Tests/Power Measurements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Comnet\Molenet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faruk\OneDrive\Desktop\Molenet Local\MoleNet V7.0\V7.0 Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6BC4FD-956C-46C3-A670-2A6C976CD6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A2509B-7CFD-44B1-851E-FAEB92570D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6559B9A0-D43C-4931-B18D-1D3B307AD1D9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6559B9A0-D43C-4931-B18D-1D3B307AD1D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
-  <si>
-    <t>Device</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="39">
   <si>
     <t>Idle</t>
   </si>
@@ -47,9 +44,6 @@
     <t>Lightsleep</t>
   </si>
   <si>
-    <t xml:space="preserve"> deepsleep</t>
-  </si>
-  <si>
     <t>Molenet Board</t>
   </si>
   <si>
@@ -80,9 +74,6 @@
     <t>No Read and write operation. It needs to be checked additionally</t>
   </si>
   <si>
-    <t>No data requested rom BME</t>
-  </si>
-  <si>
     <t>37.7 mA</t>
   </si>
   <si>
@@ -99,6 +90,69 @@
   </si>
   <si>
     <t>128 uA</t>
+  </si>
+  <si>
+    <t>No data requested from BME</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Deepsleep</t>
+  </si>
+  <si>
+    <t>Device=Molenet V7.0</t>
+  </si>
+  <si>
+    <t>Device=Molenet V6.3</t>
+  </si>
+  <si>
+    <t>32 mA</t>
+  </si>
+  <si>
+    <t>1.4 mA</t>
+  </si>
+  <si>
+    <t>140uA</t>
+  </si>
+  <si>
+    <t>35 mA</t>
+  </si>
+  <si>
+    <t>3.9 mA</t>
+  </si>
+  <si>
+    <t>2.5 mA</t>
+  </si>
+  <si>
+    <t>41 mA</t>
+  </si>
+  <si>
+    <t>10 mA</t>
+  </si>
+  <si>
+    <t>8.7 mA</t>
+  </si>
+  <si>
+    <t>Device=Molenet V6.1</t>
+  </si>
+  <si>
+    <t>34 mA</t>
+  </si>
+  <si>
+    <t>1 mA</t>
+  </si>
+  <si>
+    <t>80 uA</t>
+  </si>
+  <si>
+    <t>2.8 mA</t>
+  </si>
+  <si>
+    <t>40 mA</t>
+  </si>
+  <si>
+    <t>9.4 mA</t>
+  </si>
+  <si>
+    <t>8.4 mA</t>
   </si>
 </sst>
 </file>
@@ -114,15 +168,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -130,12 +190,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3EE43B-6B53-481F-B852-BD1C0FA1AE01}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.44140625" bestFit="1" customWidth="1"/>
@@ -480,97 +557,292 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="E17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
